--- a/i18n/lt.xlsx
+++ b/i18n/lt.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -4619,123 +4619,72 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
     <t>[bird] ŠIOJE [forest]</t>
   </si>
   <si>
     <t>Suskaičiuokite visus paukščius, kuriuos šiuo metu turite &lt;b&gt;šios konkrečios buveinės eilėje&lt;/b&gt;.&lt;br&gt;&lt;i&gt;Po tokį tikslą turi kiekviena buveinė.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
     <t>[bird] ŠIOJE [grassland]</t>
   </si>
   <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
     <t>[bird] ŠIOJE [wetland]</t>
   </si>
   <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
     <t>[egg] ŠIOJE [forest]</t>
   </si>
   <si>
     <t>Suskaičiuokite visus kiaušinius, kuriuos jūsų paukščiai padėjo &lt;b&gt;šios konkrečios buveinės eilėje&lt;/b&gt;. Skaičiuojami visi ant kiekvieno paukščio esantys kiaušiniai.&lt;br&gt;&lt;i&gt;Po tokį tikslą turi kiekviena buveinė.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
     <t>[egg] ŠIOJE [grassland]</t>
   </si>
   <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
     <t>[egg] ŠIOJE [wetland]</t>
   </si>
   <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[cavity] [bird] SU [egg]</t>
   </si>
   <si>
     <t>Suskaičiuokite visus &lt;b&gt;paukščius su šia konkrečia lizdo rūšimi&lt;/b&gt;, ant kurių padėtas bent 1 kiaušinis. Kiekvienas paukštis skaičiuojamas tik vieną kartą – nesvarbu, kiek kiaušinių jis turi. Prie šio tikslo įskaitomi ir lizdai su žvaigždutės simboliu.&lt;br&gt;&lt;i&gt;Po tokį tikslą turi kiekviena lizdo rūšis.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[bowl] [bird] SU [egg]</t>
   </si>
   <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[ground] [bird] SU [egg]</t>
   </si>
   <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
     <t>[platform] [bird] SU [egg]</t>
   </si>
   <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
     <t>[egg] ŠIAME [cavity]</t>
   </si>
   <si>
     <t>Suskaičiuokite visus kiaušinius, padėtus ant paukščių &lt;b&gt;su šia konkrečia lizdo rūšimi&lt;/b&gt;. Skaičiuojami visi ant paukščio esantys kiaušiniai. Prie šio tikslo įskaitomi ir lizdai su žvaigždutės simboliu.&lt;br&gt;&lt;i&gt;Po tokį tikslą turi kiekviena lizdo rūšis.&lt;/i&gt;</t>
   </si>
   <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
     <t>[egg] ŠIAME [bowl]</t>
   </si>
   <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
     <t>[egg] ŠIAME [ground]</t>
   </si>
   <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
     <t>[egg] ŠIAME [platform]</t>
   </si>
   <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
     <t>[egg][egg][egg] RINKINIAI ŠIOSE [wetland][grassland][forest]</t>
   </si>
   <si>
     <t>Vieną kiaušinių rinkinį sudaro 1 kiaušinis šlapynės eilėje, 1 kiaušinis pievos eilėje ir 1 kiaušinis miško eilėje. Suskaičiuokite rinkinių skaičių.</t>
   </si>
   <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
     <t>IŠ VISO [bird]</t>
   </si>
   <si>
     <t>Suskaičiuokite bendrą padėtų paukščių skaičių.</t>
   </si>
   <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Turimas maistas</t>
   </si>
   <si>
@@ -4755,9 +4704,6 @@
   </si>
   <si>
     <t>Jūsų rankoje turimų paukščių kortų skaičius.</t>
-  </si>
-  <si>
-    <t>Birds Worth over 4 Points</t>
   </si>
   <si>
     <t>Paukščiai, kurių vertė yra daugiau nei 4 taškai</t>
@@ -4768,7 +4714,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">[bird], KURIŲ VERTĖ </t>
     </r>
@@ -4777,6 +4724,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>&gt;4[point]</t>
     </r>
@@ -4785,9 +4734,6 @@
     <t>Jūsų padėtų paukščių, kurių nurodyta vertė taškais didesnė nei 4, skaičius.</t>
   </si>
   <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
     <t>Paukščiai be kiaušinių</t>
   </si>
   <si>
@@ -4797,9 +4743,6 @@
     <t>Jūsų padėtų paukščių, ant kurių nėra nė vieno kiaušinio, skaičius, kai už šį tikslą skaičiuojami taškai.</t>
   </si>
   <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
     <t>Paukščiai vienoje eilėje</t>
   </si>
   <si>
@@ -4809,9 +4752,6 @@
     <t>Jūsų padėtų paukščių skaičius buveinėje, kurioje yra daugiausiai paukščių.</t>
   </si>
   <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
     <t>Užpildyti stulpeliai</t>
   </si>
   <si>
@@ -4821,9 +4761,6 @@
     <t>Stulpelių, kuriuose užpildyti visi trys paukščiams skirti laukeliai, skaičius.</t>
   </si>
   <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
     <t>Rudos galios</t>
   </si>
   <si>
@@ -4833,163 +4770,229 @@
     <t>Jūsų padėtų paukščių, turinčių rudas „Aktyvavus“ galias, skaičius.</t>
   </si>
   <si>
-    <t>White &amp; No Powers</t>
+    <t>BALTA GALIA IR BE GALIOS</t>
+  </si>
+  <si>
+    <t>Jūsų padėtų paukščių, neturinčių galios arba turinčių „Padėjus“ galią, skaičius.&lt;br&gt;&lt;i&gt;* Pagrindiniame žaidime ši galia vadinama „bespalve“.</t>
+  </si>
+  <si>
+    <t>[flocking] PAUKŠČIAI SU PAKIŠTOMIS KORTOMIS</t>
+  </si>
+  <si>
+    <t>Jūsų padėtų paukščių, kurie turi bent 1 pakištą kortą, skaičius.</t>
+  </si>
+  <si>
+    <t>Padėtų paukščių kaina maistu</t>
+  </si>
+  <si>
+    <t>PADĖTŲ [bird] KAINA MAISTU</t>
+  </si>
+  <si>
+    <t>Suskaičiuokite savo paukščių kainą maistu; tiems paukščiams, kurių kaina maistu gali būti pasirenkama, nepamirškite skaičiuoti tik 1 maisto simbolį.</t>
+  </si>
+  <si>
+    <t>Translated</t>
+  </si>
+  <si>
+    <t>WHEN ACTIVATED</t>
+  </si>
+  <si>
+    <t>AKTYVAVUS</t>
+  </si>
+  <si>
+    <t>WHEN PLAYED</t>
+  </si>
+  <si>
+    <t>PADĖJUS</t>
+  </si>
+  <si>
+    <t>ONCE BETWEEN TURNS</t>
+  </si>
+  <si>
+    <t>KARTĄ TARP ĖJIMŲ</t>
+  </si>
+  <si>
+    <t>ROUND END</t>
+  </si>
+  <si>
+    <t>BAIGUS RAUNDĄ</t>
+  </si>
+  <si>
+    <t>GAME END</t>
+  </si>
+  <si>
+    <t>BAIGUS ŽAIDIMĄ</t>
+  </si>
+  <si>
+    <t>of cards</t>
+  </si>
+  <si>
+    <t>kortų</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Show bonus cards match symbols</t>
+  </si>
+  <si>
+    <t>Black-Bellied Whistling-Duck</t>
+  </si>
+  <si>
+    <t>Eastern Screech-Owl</t>
+  </si>
+  <si>
+    <t>Many-Colored Fruit-Dove</t>
+  </si>
+  <si>
+    <t>Greater Prairie-Chicken</t>
+  </si>
+  <si>
+    <t>Phasianus colchicus versicolor</t>
+  </si>
+  <si>
+    <t>Kākāpō</t>
+  </si>
+  <si>
+    <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
   <si>
     <t>Balta* galia ir be galios</t>
-  </si>
-  <si>
-    <t>BALTA GALIA IR BE GALIOS</t>
-  </si>
-  <si>
-    <t>Jūsų padėtų paukščių, neturinčių galios arba turinčių „Padėjus“ galią, skaičius.&lt;br&gt;&lt;i&gt;* Pagrindiniame žaidime ši galia vadinama „bespalve“.</t>
-  </si>
-  <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
-    <t>[flocking] PAUKŠČIAI SU PAKIŠTOMIS KORTOMIS</t>
-  </si>
-  <si>
-    <t>Jūsų padėtų paukščių, kurie turi bent 1 pakištą kortą, skaičius.</t>
-  </si>
-  <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
-    <t>Padėtų paukščių kaina maistu</t>
-  </si>
-  <si>
-    <t>PADĖTŲ [bird] KAINA MAISTU</t>
-  </si>
-  <si>
-    <t>Suskaičiuokite savo paukščių kainą maistu; tiems paukščiams, kurių kaina maistu gali būti pasirenkama, nepamirškite skaičiuoti tik 1 maisto simbolį.</t>
-  </si>
-  <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>No Goal</t>
-  </si>
-  <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
-  </si>
-  <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
-    <t>In Forest</t>
-  </si>
-  <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
-    <t>Translated</t>
-  </si>
-  <si>
-    <t>WHEN ACTIVATED</t>
-  </si>
-  <si>
-    <t>AKTYVAVUS</t>
-  </si>
-  <si>
-    <t>WHEN PLAYED</t>
-  </si>
-  <si>
-    <t>PADĖJUS</t>
-  </si>
-  <si>
-    <t>ONCE BETWEEN TURNS</t>
-  </si>
-  <si>
-    <t>KARTĄ TARP ĖJIMŲ</t>
-  </si>
-  <si>
-    <t>ROUND END</t>
-  </si>
-  <si>
-    <t>BAIGUS RAUNDĄ</t>
-  </si>
-  <si>
-    <t>GAME END</t>
-  </si>
-  <si>
-    <t>BAIGUS ŽAIDIMĄ</t>
-  </si>
-  <si>
-    <t>of cards</t>
-  </si>
-  <si>
-    <t>kortų</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Show bonus cards match symbols</t>
-  </si>
-  <si>
-    <t>Black-Bellied Whistling-Duck</t>
-  </si>
-  <si>
-    <t>Eastern Screech-Owl</t>
-  </si>
-  <si>
-    <t>Many-Colored Fruit-Dove</t>
-  </si>
-  <si>
-    <t>Greater Prairie-Chicken</t>
-  </si>
-  <si>
-    <t>Phasianus colchicus versicolor</t>
-  </si>
-  <si>
-    <t>Kākāpō</t>
-  </si>
-  <si>
-    <t>Flavor text</t>
   </si>
 </sst>
 </file>
@@ -5031,12 +5034,8 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
@@ -5049,13 +5048,21 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5078,7 +5085,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
@@ -5095,12 +5102,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -5387,7 +5395,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>1628</v>
+        <v>1582</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -6246,7 +6254,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>1622</v>
+        <v>1576</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>154</v>
@@ -8064,7 +8072,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1623</v>
+        <v>1577</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>424</v>
@@ -8873,7 +8881,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1625</v>
+        <v>1579</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>550</v>
@@ -12530,7 +12538,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="14" t="s">
-        <v>1627</v>
+        <v>1581</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>1042</v>
@@ -12729,7 +12737,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>1624</v>
+        <v>1578</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>1069</v>
@@ -14026,7 +14034,7 @@
         <v>1243</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>1626</v>
+        <v>1580</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>1162</v>
@@ -15880,17 +15888,17 @@
         <v>2000</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1510</v>
+        <v>1583</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="9" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>1511</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15898,17 +15906,17 @@
         <v>2001</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>1513</v>
+        <v>1584</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="9" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15916,17 +15924,17 @@
         <v>2002</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1515</v>
+        <v>1585</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="9" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15934,17 +15942,17 @@
         <v>2013</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1517</v>
+        <v>1586</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15952,17 +15960,17 @@
         <v>2014</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1520</v>
+        <v>1587</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15970,17 +15978,17 @@
         <v>2017</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1522</v>
+        <v>1588</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="9" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -15988,17 +15996,17 @@
         <v>2010</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1524</v>
+        <v>1589</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16006,17 +16014,17 @@
         <v>2008</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>1527</v>
+        <v>1590</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="9" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16024,17 +16032,17 @@
         <v>2021</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1529</v>
+        <v>1591</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="9" t="s">
-        <v>1530</v>
+        <v>1521</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16042,17 +16050,17 @@
         <v>2022</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1531</v>
+        <v>1592</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="9" t="s">
-        <v>1532</v>
+        <v>1522</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16060,17 +16068,17 @@
         <v>2012</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1533</v>
+        <v>1593</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="9" t="s">
-        <v>1534</v>
+        <v>1523</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>1535</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16078,17 +16086,17 @@
         <v>2011</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1536</v>
+        <v>1594</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="9" t="s">
-        <v>1537</v>
+        <v>1525</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>1535</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16096,17 +16104,17 @@
         <v>2015</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1538</v>
+        <v>1595</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="9" t="s">
-        <v>1539</v>
+        <v>1526</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>1535</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16114,17 +16122,17 @@
         <v>2016</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1540</v>
+        <v>1596</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="9" t="s">
-        <v>1541</v>
+        <v>1527</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>1535</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16132,17 +16140,17 @@
         <v>2023</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1542</v>
+        <v>1597</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="9" t="s">
-        <v>1543</v>
+        <v>1528</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>1544</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16150,17 +16158,17 @@
         <v>2024</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1545</v>
+        <v>1598</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="9" t="s">
-        <v>1546</v>
+        <v>1530</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>1547</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16168,19 +16176,19 @@
         <v>2020</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1548</v>
+        <v>1599</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1549</v>
+        <v>1532</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>1550</v>
+        <v>1533</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>1551</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16188,19 +16196,19 @@
         <v>2003</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1552</v>
+        <v>1535</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1553</v>
+        <v>1536</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>1554</v>
+        <v>1537</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>1555</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16208,19 +16216,19 @@
         <v>2004</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1556</v>
+        <v>1600</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1557</v>
+        <v>1539</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>1558</v>
+        <v>1540</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>1559</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16228,19 +16236,19 @@
         <v>2006</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1560</v>
+        <v>1601</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1561</v>
+        <v>1542</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1562</v>
+        <v>1543</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1563</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16248,19 +16256,19 @@
         <v>2005</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1564</v>
+        <v>1602</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1565</v>
+        <v>1545</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>1566</v>
+        <v>1546</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>1567</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16268,19 +16276,19 @@
         <v>2018</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1568</v>
+        <v>1603</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1569</v>
+        <v>1548</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>1570</v>
+        <v>1549</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>1571</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16288,19 +16296,19 @@
         <v>2009</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1572</v>
+        <v>1604</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1573</v>
+        <v>1551</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>1574</v>
+        <v>1552</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>1575</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16308,19 +16316,19 @@
         <v>2025</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1576</v>
+        <v>1605</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1577</v>
+        <v>1628</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>1578</v>
+        <v>1554</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>1579</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16328,7 +16336,7 @@
         <v>2007</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1580</v>
+        <v>1606</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>89</v>
@@ -16337,10 +16345,10 @@
         <v>1472</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>1581</v>
+        <v>1556</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>1582</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16348,19 +16356,19 @@
         <v>2019</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1583</v>
+        <v>1607</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1584</v>
+        <v>1558</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1585</v>
+        <v>1559</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>1586</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -16368,7 +16376,7 @@
         <v>2031</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1587</v>
+        <v>1608</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>973</v>
@@ -16382,7 +16390,7 @@
         <v>2030</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1588</v>
+        <v>1609</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>973</v>
@@ -16396,7 +16404,7 @@
         <v>2033</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1589</v>
+        <v>1610</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>973</v>
@@ -16410,7 +16418,7 @@
         <v>2032</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1590</v>
+        <v>1611</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>973</v>
@@ -16424,7 +16432,7 @@
         <v>2026</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1591</v>
+        <v>1612</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>973</v>
@@ -16438,7 +16446,7 @@
         <v>2027</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1592</v>
+        <v>1613</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>973</v>
@@ -16452,7 +16460,7 @@
         <v>2029</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1593</v>
+        <v>1614</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>973</v>
@@ -16466,7 +16474,7 @@
         <v>2028</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>1594</v>
+        <v>1615</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>973</v>
@@ -16479,8 +16487,8 @@
       <c r="A36" s="8">
         <v>2043</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>1595</v>
+      <c r="B36" s="16" t="s">
+        <v>1616</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>1162</v>
@@ -16494,7 +16502,7 @@
         <v>2040</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>1596</v>
+        <v>1617</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>1162</v>
@@ -16508,7 +16516,7 @@
         <v>2035</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1597</v>
+        <v>1618</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>1162</v>
@@ -16522,7 +16530,7 @@
         <v>2041</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>1598</v>
+        <v>1619</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>1162</v>
@@ -16536,7 +16544,7 @@
         <v>2042</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>1599</v>
+        <v>1620</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>1162</v>
@@ -16550,7 +16558,7 @@
         <v>2044</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1600</v>
+        <v>1621</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>1162</v>
@@ -16564,7 +16572,7 @@
         <v>2036</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1601</v>
+        <v>1622</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>1162</v>
@@ -16578,7 +16586,7 @@
         <v>2034</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>1602</v>
+        <v>1623</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>1162</v>
@@ -16592,7 +16600,7 @@
         <v>2037</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>1603</v>
+        <v>1624</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>1162</v>
@@ -16606,7 +16614,7 @@
         <v>2038</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>1604</v>
+        <v>1625</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>1162</v>
@@ -16620,7 +16628,7 @@
         <v>2039</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>1605</v>
+        <v>1626</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>1162</v>
@@ -16634,7 +16642,7 @@
         <v>2045</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1606</v>
+        <v>1627</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>1162</v>
@@ -16668,55 +16676,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1607</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1608</v>
+        <v>1562</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1609</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1610</v>
+        <v>1564</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1611</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1612</v>
+        <v>1566</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1613</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1614</v>
+        <v>1568</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1615</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1616</v>
+        <v>1570</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1617</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1618</v>
+        <v>1572</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1619</v>
+        <v>1573</v>
       </c>
     </row>
   </sheetData>
@@ -16742,12 +16750,12 @@
         <v>1340</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>1620</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1621</v>
+        <v>1575</v>
       </c>
       <c r="B2" s="11" t="b">
         <f>FALSE()</f>
